--- a/public/sap-reporting/expansion-150-downloads/EXT-MM22-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-MM22-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R27a42df2270b4513"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R5a7b885495f04994"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="Rcdf81086864944bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R29f6b1bec27047eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R22f09d5873354a5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R8871d9aa67a54563"/>
   </x:sheets>
 </x:workbook>
 </file>
